--- a/文本分析/BERTopic/临川浮梦/InteractiveSheet_2026-04-07临川浮梦.xlsx
+++ b/文本分析/BERTopic/临川浮梦/InteractiveSheet_2026-04-07临川浮梦.xlsx
@@ -1533,6 +1533,12 @@
   </sheetPr>
   <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="12.6272727272727" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.81818181818182" customWidth="1"/>
+    <col min="2" max="2" width="6.54545454545455" customWidth="1"/>
+    <col min="3" max="3" width="25.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="36.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
